--- a/data/trans_camb/P57_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Habitat-trans_camb.xlsx
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,12; 17,99</t>
+          <t>6,72; 18,52</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,33; 18,61</t>
+          <t>9,55; 18,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,93; 17,02</t>
+          <t>9,35; 16,56</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,8; 65,45</t>
+          <t>20,54; 66,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,73; 77,96</t>
+          <t>32,89; 78,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,6; 63,69</t>
+          <t>30,95; 62,69</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,1; 48,5</t>
+          <t>18,57; 51,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,1; 19,63</t>
+          <t>11,77; 20,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 40,63</t>
+          <t>17,17; 41,95</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,33; 179,44</t>
+          <t>60,75; 183,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,31; 83,55</t>
+          <t>40,32; 81,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59,86; 152,17</t>
+          <t>60,02; 151,81</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,13; 29,69</t>
+          <t>19,17; 29,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 23,34</t>
+          <t>-7,44; 23,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 24,5</t>
+          <t>-0,4; 24,01</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59,16; 111,11</t>
+          <t>57,11; 107,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,96; 92,45</t>
+          <t>-24,88; 92,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 89,96</t>
+          <t>-0,53; 88,56</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,01; 14,15</t>
+          <t>4,65; 14,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 11,4</t>
+          <t>0,47; 11,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 11,51</t>
+          <t>3,65; 11,53</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>14,69; 47,25</t>
+          <t>13,74; 48,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,26; 46,26</t>
+          <t>1,72; 48,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 41,82</t>
+          <t>12,25; 41,17</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,8; 32,13</t>
+          <t>15,76; 31,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 15,1</t>
+          <t>4,29; 14,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,05; 22,01</t>
+          <t>12,08; 22,04</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>51,38; 107,58</t>
+          <t>51,28; 108,38</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>18,02; 58,73</t>
+          <t>17,91; 58,37</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42,34; 79,69</t>
+          <t>42,32; 78,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P57_R2-Habitat-trans_camb.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>12,51</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14,0</t>
+          <t>13,6</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13,22</t>
+          <t>12,81</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 18,52</t>
+          <t>6,48; 17,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,55; 18,56</t>
+          <t>9,14; 18,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,35; 16,56</t>
+          <t>9,2; 16,49</t>
         </is>
       </c>
     </row>
@@ -594,17 +594,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -617,17 +617,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,54; 66,65</t>
+          <t>20,04; 64,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,89; 78,88</t>
+          <t>31,31; 76,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,95; 62,69</t>
+          <t>30,5; 62,29</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>30,47</t>
+          <t>19,62</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15,98</t>
+          <t>15,31</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24,23</t>
+          <t>17,45</t>
         </is>
       </c>
     </row>
@@ -667,17 +667,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,57; 51,75</t>
+          <t>14,81; 23,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,77; 20,15</t>
+          <t>11,27; 19,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>17,17; 41,95</t>
+          <t>14,54; 20,22</t>
         </is>
       </c>
     </row>
@@ -690,17 +690,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>103,72%</t>
+          <t>66,79%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>62,65%</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>60,75; 183,66</t>
+          <t>47,81; 88,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>40,32; 81,31</t>
+          <t>39,96; 79,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,02; 151,81</t>
+          <t>49,51; 76,81</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>24,47</t>
+          <t>23,37</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>23,5</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16,45</t>
+          <t>23,46</t>
         </is>
       </c>
     </row>
@@ -763,17 +763,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,17; 29,86</t>
+          <t>17,66; 29,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 23,02</t>
+          <t>18,78; 28,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 24,01</t>
+          <t>19,79; 26,99</t>
         </is>
       </c>
     </row>
@@ -786,17 +786,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>57,11; 107,98</t>
+          <t>52,61; 105,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 92,9</t>
+          <t>66,48; 121,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 88,56</t>
+          <t>67,22; 103,99</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>9,46</t>
+          <t>9,03</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,09</t>
+          <t>9,16</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>9,08</t>
         </is>
       </c>
     </row>
@@ -859,17 +859,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,65; 14,4</t>
+          <t>4,53; 13,7</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,47; 11,8</t>
+          <t>5,61; 13,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 11,53</t>
+          <t>5,99; 12,09</t>
         </is>
       </c>
     </row>
@@ -882,17 +882,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>31,01%</t>
         </is>
       </c>
     </row>
@@ -905,17 +905,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13,74; 48,06</t>
+          <t>13,17; 45,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 48,0</t>
+          <t>19,35; 53,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,25; 41,17</t>
+          <t>19,07; 43,6</t>
         </is>
       </c>
     </row>
@@ -932,17 +932,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>20,29</t>
+          <t>16,05</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>11,62</t>
+          <t>14,92</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>15,83</t>
+          <t>15,46</t>
         </is>
       </c>
     </row>
@@ -955,17 +955,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,76; 31,46</t>
+          <t>13,37; 18,51</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,29; 14,96</t>
+          <t>12,95; 17,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12,08; 22,04</t>
+          <t>13,87; 17,16</t>
         </is>
       </c>
     </row>
@@ -978,17 +978,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>51,28; 108,38</t>
+          <t>42,61; 63,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>17,91; 58,37</t>
+          <t>46,78; 67,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42,32; 78,95</t>
+          <t>47,31; 62,93</t>
         </is>
       </c>
     </row>
